--- a/exports/NYKAA_full_report.xlsx
+++ b/exports/NYKAA_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:U69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>4.81</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>335.25</v>
+        <v>299.45</v>
       </c>
       <c r="I2" t="n">
         <v>330.3640923951073</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>0.18</v>
+        <v>-10.52</v>
       </c>
       <c r="L2" t="n">
-        <v>3.45</v>
+        <v>13.31</v>
       </c>
       <c r="M2" t="n">
-        <v>0.98</v>
+        <v>1.82</v>
       </c>
       <c r="N2" t="n">
-        <v>1.71</v>
+        <v>13.2</v>
       </c>
       <c r="O2" t="n">
         <v>-0.09</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>13.84</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44595.55208333334</v>
+        <v>44596.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>303.4</v>
+        <v>308.3</v>
       </c>
       <c r="I3" t="n">
         <v>306.3846803704153</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.32</v>
+        <v>-2.96</v>
       </c>
       <c r="L3" t="n">
         <v>10.65</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>11.25</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44602.55208333334</v>
+        <v>44603.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>285.05</v>
+        <v>275.6</v>
       </c>
       <c r="I4" t="n">
         <v>282.0056249784471</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>-7.54</v>
+        <v>-10.61</v>
       </c>
       <c r="L4" t="n">
-        <v>8.369999999999999</v>
+        <v>12.42</v>
       </c>
       <c r="M4" t="n">
         <v>4.11</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>12.04</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44622.55208333334</v>
+        <v>44623.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>235.15</v>
+        <v>250.8</v>
       </c>
       <c r="I5" t="n">
         <v>241.2826028496007</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K5" t="n">
-        <v>14.68</v>
+        <v>9</v>
       </c>
       <c r="L5" t="n">
         <v>3.56</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>15.08</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44673.55208333334</v>
+        <v>44676.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>307.15</v>
+        <v>291.85</v>
       </c>
       <c r="I6" t="n">
         <v>294.2331788843554</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>50.16666666666666</v>
+        <v>53</v>
       </c>
       <c r="K6" t="n">
-        <v>22.47</v>
+        <v>16.37</v>
       </c>
       <c r="L6" t="n">
         <v>11.54</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>10.88</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44697.55208333334</v>
+        <v>44698.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>238.5</v>
+        <v>245</v>
       </c>
       <c r="I7" t="n">
         <v>240.6146969158393</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K7" t="n">
-        <v>18.28</v>
+        <v>16.05</v>
       </c>
       <c r="L7" t="n">
         <v>3.94</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>16.33</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44791.55208333334</v>
+        <v>44792.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>231</v>
+        <v>228.85</v>
       </c>
       <c r="I8" t="n">
         <v>230.4823547822208</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>93.16666666666667</v>
+        <v>94</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.71</v>
+        <v>-6.59</v>
       </c>
       <c r="L8" t="n">
         <v>10.76</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>132</v>
+        <v>133</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>6.31</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44834.55208333334</v>
+        <v>44837.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>212.5</v>
+        <v>226.05</v>
       </c>
       <c r="I9" t="n">
         <v>224.8217485433483</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K9" t="n">
-        <v>7.14</v>
+        <v>1.22</v>
       </c>
       <c r="L9" t="n">
         <v>3.04</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>10.7</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44847.55208333334</v>
+        <v>44848.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>203.5</v>
+        <v>201.45</v>
       </c>
       <c r="I10" t="n">
         <v>201.857147217751</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K10" t="n">
-        <v>-9.98</v>
+        <v>-10.88</v>
       </c>
       <c r="L10" t="n">
-        <v>10.95</v>
+        <v>10.97</v>
       </c>
       <c r="M10" t="n">
         <v>1.12</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>8.27</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44865.38541666666</v>
+        <v>44865.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>178.8</v>
+        <v>196.7</v>
       </c>
       <c r="I11" t="n">
         <v>181.0801252105736</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>11.24</v>
+        <v>2.36</v>
       </c>
       <c r="L11" t="n">
         <v>2.16</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>17.21</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44874.38541666666</v>
+        <v>44874.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>183.6</v>
+        <v>173.35</v>
       </c>
       <c r="I12" t="n">
         <v>174.9218637214919</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>8.833333333333334</v>
+        <v>9</v>
       </c>
       <c r="K12" t="n">
-        <v>-6.66</v>
+        <v>-11.87</v>
       </c>
       <c r="L12" t="n">
-        <v>9.789999999999999</v>
+        <v>12.05</v>
       </c>
       <c r="M12" t="n">
         <v>0.86</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>15.11</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44875.55208333334</v>
+        <v>44876.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>185.8</v>
+        <v>208.95</v>
       </c>
       <c r="I13" t="n">
         <v>199.5431253599362</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>-7.18</v>
+        <v>-20.54</v>
       </c>
       <c r="L13" t="n">
-        <v>10.53</v>
+        <v>28.99</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N13" t="n">
-        <v>7.18</v>
+        <v>11.76</v>
       </c>
       <c r="O13" t="n">
         <v>-8.109999999999999</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>18.54</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44886.55208333334</v>
+        <v>44887.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>183.5</v>
+        <v>176.8</v>
       </c>
       <c r="I14" t="n">
         <v>180.0416420155902</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K14" t="n">
-        <v>-12.18</v>
+        <v>-15.39</v>
       </c>
       <c r="L14" t="n">
         <v>18.04</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>18.82</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44924.38541666666</v>
+        <v>44924.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>150.05</v>
+        <v>158.65</v>
       </c>
       <c r="I15" t="n">
         <v>157.073275262232</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>37</v>
+        <v>37.16666666666666</v>
       </c>
       <c r="K15" t="n">
-        <v>15.13</v>
+        <v>10.27</v>
       </c>
       <c r="L15" t="n">
         <v>5.51</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>11.41</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44939.55208333334</v>
+        <v>44942.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>147.4</v>
+        <v>140.6</v>
       </c>
       <c r="I16" t="n">
         <v>145.8799362996473</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>15</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K16" t="n">
-        <v>-7.09</v>
+        <v>-11.38</v>
       </c>
       <c r="L16" t="n">
-        <v>7.78</v>
+        <v>11.69</v>
       </c>
       <c r="M16" t="n">
         <v>0.97</v>
       </c>
       <c r="N16" t="n">
-        <v>3.54</v>
+        <v>5.02</v>
       </c>
       <c r="O16" t="n">
         <v>5.42</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,25 +1592,25 @@
         <v>10.3</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44956.55208333334</v>
+        <v>44958.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>131.05</v>
+        <v>140</v>
       </c>
       <c r="I17" t="n">
         <v>137.2996983694071</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K17" t="n">
-        <v>6.79</v>
+        <v>0.43</v>
       </c>
       <c r="L17" t="n">
         <v>5.48</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1</v>
+        <v>4.54</v>
       </c>
       <c r="N17" t="n">
         <v>7.74</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>12.95</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44972.55208333334</v>
+        <v>44973.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>143.2</v>
+        <v>139.3</v>
       </c>
       <c r="I18" t="n">
         <v>140.1972953940116</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K18" t="n">
-        <v>2.29</v>
+        <v>-0.5</v>
       </c>
       <c r="L18" t="n">
         <v>4.86</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>12.28</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45019.55208333334</v>
+        <v>45021.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>128</v>
+        <v>137.05</v>
       </c>
       <c r="I19" t="n">
         <v>133.7762200129499</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>46.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K19" t="n">
-        <v>8.109999999999999</v>
+        <v>1.62</v>
       </c>
       <c r="L19" t="n">
         <v>8.26</v>
@@ -1524,7 +1751,7 @@
         <v>1.47</v>
       </c>
       <c r="N19" t="n">
-        <v>3.4</v>
+        <v>6.56</v>
       </c>
       <c r="O19" t="n">
         <v>-2.86</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>12.37</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45035.55208333334</v>
+        <v>45036.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>124.45</v>
+        <v>123.75</v>
       </c>
       <c r="I20" t="n">
         <v>124.0546106105596</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K20" t="n">
-        <v>-9.19</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>9.52</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="M20" t="n">
         <v>0.08</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>5.26</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45043.55208333334</v>
+        <v>45044.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>116</v>
+        <v>123.95</v>
       </c>
       <c r="I21" t="n">
         <v>122.5307787746761</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K21" t="n">
-        <v>6.26</v>
+        <v>-0.16</v>
       </c>
       <c r="L21" t="n">
         <v>0.8100000000000001</v>
@@ -1638,7 +1889,7 @@
         <v>1.57</v>
       </c>
       <c r="N21" t="n">
-        <v>0.09</v>
+        <v>5.22</v>
       </c>
       <c r="O21" t="n">
         <v>-0.4</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>11.38</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45114.38541666666</v>
+        <v>45114.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>142.85</v>
+        <v>140.45</v>
       </c>
       <c r="I22" t="n">
         <v>140.6123104267629</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>70</v>
+        <v>70.16666666666667</v>
       </c>
       <c r="K22" t="n">
-        <v>15.25</v>
+        <v>13.31</v>
       </c>
       <c r="L22" t="n">
         <v>7.34</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>7.16</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45174.55208333334</v>
+        <v>45175.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>138.8</v>
+        <v>142.65</v>
       </c>
       <c r="I23" t="n">
         <v>139.6367344981383</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>60</v>
+        <v>60.83333333333334</v>
       </c>
       <c r="K23" t="n">
-        <v>1.17</v>
+        <v>-1.57</v>
       </c>
       <c r="L23" t="n">
         <v>9.18</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,25 +2075,25 @@
         <v>7.16</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45189.55208333334</v>
+        <v>45190.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>145.2</v>
+        <v>141</v>
       </c>
       <c r="I24" t="n">
         <v>143.5223117129688</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K24" t="n">
-        <v>1.79</v>
+        <v>-1.16</v>
       </c>
       <c r="L24" t="n">
         <v>3.75</v>
       </c>
       <c r="M24" t="n">
-        <v>0.37</v>
+        <v>0.83</v>
       </c>
       <c r="N24" t="n">
         <v>3</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>8.08</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45197.38541666666</v>
+        <v>45197.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>147.7</v>
+        <v>153.2</v>
       </c>
       <c r="I25" t="n">
         <v>151.1573654409482</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.75</v>
+        <v>-8.65</v>
       </c>
       <c r="L25" t="n">
-        <v>6.24</v>
+        <v>12.06</v>
       </c>
       <c r="M25" t="n">
         <v>0.33</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>7.5</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45218.55208333334</v>
+        <v>45219.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>144.65</v>
+        <v>142.75</v>
       </c>
       <c r="I26" t="n">
         <v>143.025265493805</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>21</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>-5.58</v>
+        <v>-6.82</v>
       </c>
       <c r="L26" t="n">
-        <v>6.49</v>
+        <v>6.89</v>
       </c>
       <c r="M26" t="n">
         <v>2.29</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>5.68</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45236.38541666666</v>
+        <v>45236.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>146.45</v>
+        <v>147.45</v>
       </c>
       <c r="I27" t="n">
         <v>147.0032920140682</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.59</v>
+        <v>-3.29</v>
       </c>
       <c r="L27" t="n">
-        <v>3.26</v>
+        <v>3.68</v>
       </c>
       <c r="M27" t="n">
         <v>1.21</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>5.54</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>172.75</v>
+        <v>162.45</v>
       </c>
       <c r="I28" t="n">
         <v>166.1638058461693</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>43.83333333333334</v>
+        <v>44</v>
       </c>
       <c r="K28" t="n">
-        <v>17.16</v>
+        <v>10.17</v>
       </c>
       <c r="L28" t="n">
         <v>1.53</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>11.88</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45299.55208333334</v>
+        <v>45300.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>177</v>
+        <v>186.1</v>
       </c>
       <c r="I29" t="n">
         <v>180.5618635634864</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>-8.960000000000001</v>
+        <v>-14.56</v>
       </c>
       <c r="L29" t="n">
-        <v>12.03</v>
+        <v>17.94</v>
       </c>
       <c r="M29" t="n">
         <v>1.82</v>
       </c>
       <c r="N29" t="n">
-        <v>3.09</v>
+        <v>5.62</v>
       </c>
       <c r="O29" t="n">
         <v>-5.44</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>9.210000000000001</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45306.55208333334</v>
+        <v>45307.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>182</v>
+        <v>172.6</v>
       </c>
       <c r="I30" t="n">
         <v>177.6268840575047</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K30" t="n">
-        <v>-2.2</v>
+        <v>-7.25</v>
       </c>
       <c r="L30" t="n">
-        <v>4.81</v>
+        <v>7.44</v>
       </c>
       <c r="M30" t="n">
-        <v>0.47</v>
+        <v>1.18</v>
       </c>
       <c r="N30" t="n">
-        <v>3.11</v>
+        <v>4.84</v>
       </c>
       <c r="O30" t="n">
         <v>5.62</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>12.55</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45352.38541666666</v>
+        <v>45355.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>156.9</v>
+        <v>158.95</v>
       </c>
       <c r="I31" t="n">
         <v>157.5449044305893</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K31" t="n">
-        <v>9.1</v>
+        <v>7.91</v>
       </c>
       <c r="L31" t="n">
         <v>4.58</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>4.87</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45364.38541666666</v>
+        <v>45364.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>152.2</v>
+        <v>146.8</v>
       </c>
       <c r="I32" t="n">
         <v>151.2017340814983</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K32" t="n">
-        <v>-4.25</v>
+        <v>-7.64</v>
       </c>
       <c r="L32" t="n">
-        <v>4.72</v>
+        <v>8.59</v>
       </c>
       <c r="M32" t="n">
         <v>0.51</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>10.1</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45372.55208333334</v>
+        <v>45373.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>159</v>
+        <v>161.75</v>
       </c>
       <c r="I33" t="n">
         <v>161.6305740556132</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K33" t="n">
-        <v>-8.31</v>
+        <v>-10.18</v>
       </c>
       <c r="L33" t="n">
-        <v>9.539999999999999</v>
+        <v>10.76</v>
       </c>
       <c r="M33" t="n">
         <v>1.14</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>8.33</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45435.55208333334</v>
+        <v>45436.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>173.5</v>
+        <v>170.1</v>
       </c>
       <c r="I34" t="n">
         <v>171.5130997973862</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>62.16666666666666</v>
+        <v>63</v>
       </c>
       <c r="K34" t="n">
-        <v>7.26</v>
+        <v>5.16</v>
       </c>
       <c r="L34" t="n">
         <v>2.35</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>8.84</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45449.55208333334</v>
+        <v>45450.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>169.75</v>
+        <v>170.5</v>
       </c>
       <c r="I35" t="n">
         <v>170.0428454134594</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K35" t="n">
-        <v>0.21</v>
+        <v>-0.24</v>
       </c>
       <c r="L35" t="n">
         <v>3.12</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>8.32</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45551.55208333334</v>
+        <v>45552.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>205.99</v>
+        <v>199.98</v>
       </c>
       <c r="I36" t="n">
         <v>201.2814431703509</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>101.1666666666667</v>
+        <v>102</v>
       </c>
       <c r="K36" t="n">
-        <v>20.82</v>
+        <v>17.29</v>
       </c>
       <c r="L36" t="n">
         <v>4.05</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>138</v>
+        <v>139</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>8.539999999999999</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45603.38541666666</v>
+        <v>45603.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>187.39</v>
+        <v>192.33</v>
       </c>
       <c r="I37" t="n">
         <v>188.9184694871874</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>51</v>
+        <v>51.16666666666666</v>
       </c>
       <c r="K37" t="n">
-        <v>6.3</v>
+        <v>3.83</v>
       </c>
       <c r="L37" t="n">
         <v>3.65</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>7.87</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45608.55208333334</v>
+        <v>45609.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>179.01</v>
+        <v>172</v>
       </c>
       <c r="I38" t="n">
         <v>177.1951092041993</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K38" t="n">
-        <v>-6.93</v>
+        <v>-10.57</v>
       </c>
       <c r="L38" t="n">
-        <v>8.880000000000001</v>
+        <v>10.94</v>
       </c>
       <c r="M38" t="n">
         <v>0.17</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>15.28</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45642.55208333334</v>
+        <v>45643.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>174.7</v>
+        <v>178.33</v>
       </c>
       <c r="I39" t="n">
         <v>176.7343216772506</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.57</v>
+        <v>-3.68</v>
       </c>
       <c r="L39" t="n">
         <v>9.300000000000001</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>7.59</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45646.55208333334</v>
+        <v>45649.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>167.91</v>
+        <v>160.57</v>
       </c>
       <c r="I40" t="n">
         <v>165.6859198797719</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K40" t="n">
-        <v>-5.84</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>6.85</v>
+        <v>10.04</v>
       </c>
       <c r="M40" t="n">
         <v>1.81</v>
       </c>
       <c r="N40" t="n">
-        <v>1.98</v>
+        <v>5.04</v>
       </c>
       <c r="O40" t="n">
         <v>1.03</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>10.82</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45660.55208333334</v>
+        <v>45663.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>168.25</v>
+        <v>175.35</v>
       </c>
       <c r="I41" t="n">
         <v>170.0163160050147</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K41" t="n">
-        <v>-4.78</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>5.74</v>
+        <v>9.98</v>
       </c>
       <c r="M41" t="n">
-        <v>0.53</v>
+        <v>4.07</v>
       </c>
       <c r="N41" t="n">
-        <v>1.45</v>
+        <v>1.99</v>
       </c>
       <c r="O41" t="n">
         <v>-5.04</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>7.35</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45678.55208333334</v>
+        <v>45679.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>168.5</v>
+        <v>163.52</v>
       </c>
       <c r="I42" t="n">
         <v>164.6620310543702</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K42" t="n">
-        <v>-3.91</v>
+        <v>-6.75</v>
       </c>
       <c r="L42" t="n">
         <v>7.81</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>8.76</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45688.55208333334</v>
+        <v>45689.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>169</v>
+        <v>176.61</v>
       </c>
       <c r="I43" t="n">
         <v>176.2423573895919</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K43" t="n">
-        <v>-3.35</v>
+        <v>-8.01</v>
       </c>
       <c r="L43" t="n">
-        <v>5.96</v>
+        <v>8.17</v>
       </c>
       <c r="M43" t="n">
         <v>0.84</v>
       </c>
       <c r="N43" t="n">
-        <v>2.74</v>
+        <v>4.14</v>
       </c>
       <c r="O43" t="n">
         <v>-1.38</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>11.77</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45709.38541666666</v>
+        <v>45709.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>164.26</v>
+        <v>163.9</v>
       </c>
       <c r="I44" t="n">
         <v>164.1552798328092</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K44" t="n">
-        <v>-6.99</v>
+        <v>-7.2</v>
       </c>
       <c r="L44" t="n">
-        <v>7.31</v>
+        <v>8.24</v>
       </c>
       <c r="M44" t="n">
         <v>0.64</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>6.87</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45722.38541666666</v>
+        <v>45722.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>167.5</v>
+        <v>169.24</v>
       </c>
       <c r="I45" t="n">
         <v>168.5904866490121</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>12.83333333333333</v>
+        <v>13</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.2</v>
+        <v>-3.26</v>
       </c>
       <c r="L45" t="n">
-        <v>2.72</v>
+        <v>3.69</v>
       </c>
       <c r="M45" t="n">
         <v>1.41</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>6.68</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45842.38541666666</v>
+        <v>45842.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>198.93</v>
+        <v>198.4</v>
       </c>
       <c r="I46" t="n">
         <v>198.8356778685848</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>119.8333333333333</v>
+        <v>120</v>
       </c>
       <c r="K46" t="n">
-        <v>17.54</v>
+        <v>17.23</v>
       </c>
       <c r="L46" t="n">
         <v>5.6</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>158</v>
+        <v>159</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>5</v>
+      </c>
+      <c r="U46" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>6.1</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45847.38541666666</v>
+        <v>45847.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>210.28</v>
+        <v>212.99</v>
       </c>
       <c r="I47" t="n">
         <v>210.5103082504215</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>4.833333333333333</v>
+        <v>5</v>
       </c>
       <c r="K47" t="n">
-        <v>-5.99</v>
+        <v>-7.35</v>
       </c>
       <c r="L47" t="n">
-        <v>6.35</v>
+        <v>8.34</v>
       </c>
       <c r="M47" t="n">
         <v>0.8100000000000001</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>6.35</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45866.38541666666</v>
+        <v>45866.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>210.53</v>
+        <v>209.87</v>
       </c>
       <c r="I48" t="n">
         <v>210.1863113383555</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>18.83333333333333</v>
+        <v>19</v>
       </c>
       <c r="K48" t="n">
-        <v>-1.15</v>
+        <v>-1.46</v>
       </c>
       <c r="L48" t="n">
-        <v>1.87</v>
+        <v>2.36</v>
       </c>
       <c r="M48" t="n">
         <v>0.65</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>4.57</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45881.55208333334</v>
+        <v>45882.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>205.7</v>
+        <v>216.21</v>
       </c>
       <c r="I49" t="n">
         <v>213.1116814983217</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K49" t="n">
-        <v>1.99</v>
+        <v>-3.02</v>
       </c>
       <c r="L49" t="n">
-        <v>2.05</v>
+        <v>5.19</v>
       </c>
       <c r="M49" t="n">
-        <v>0.53</v>
+        <v>4.52</v>
       </c>
       <c r="N49" t="n">
-        <v>1.72</v>
+        <v>4.6</v>
       </c>
       <c r="O49" t="n">
         <v>-1</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>6.7</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45925.55208333334</v>
+        <v>45926.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>236.58</v>
+        <v>232.78</v>
       </c>
       <c r="I50" t="n">
         <v>235.5294515404113</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K50" t="n">
-        <v>9.42</v>
+        <v>7.66</v>
       </c>
       <c r="L50" t="n">
         <v>2.87</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>5.77</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45933.55208333334</v>
+        <v>45936.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>238.62</v>
+        <v>252.88</v>
       </c>
       <c r="I51" t="n">
         <v>242.3117832265069</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K51" t="n">
-        <v>-2.51</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>4.09</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N51" t="n">
-        <v>3.29</v>
+        <v>7.07</v>
       </c>
       <c r="O51" t="n">
         <v>-2.09</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>8.6</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45961.38541666666</v>
+        <v>45961.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>253</v>
+        <v>248.47</v>
       </c>
       <c r="I52" t="n">
         <v>250.6390209995715</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K52" t="n">
-        <v>0.05</v>
+        <v>-1.74</v>
       </c>
       <c r="L52" t="n">
         <v>5.29</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>5.86</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45968.55208333334</v>
+        <v>45971.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>246</v>
+        <v>262.2</v>
       </c>
       <c r="I53" t="n">
         <v>258.8092614507409</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>7</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K53" t="n">
-        <v>0.99</v>
+        <v>-5.53</v>
       </c>
       <c r="L53" t="n">
-        <v>2.19</v>
+        <v>6.73</v>
       </c>
       <c r="M53" t="n">
-        <v>1.2</v>
+        <v>2.85</v>
       </c>
       <c r="N53" t="n">
-        <v>0.54</v>
+        <v>5.69</v>
       </c>
       <c r="O53" t="n">
         <v>-3.69</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>8.6</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45994.55208333334</v>
+        <v>45995.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>258.8</v>
+        <v>256.5</v>
       </c>
       <c r="I54" t="n">
         <v>257.5921987162979</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K54" t="n">
-        <v>-1.3</v>
+        <v>-2.17</v>
       </c>
       <c r="L54" t="n">
         <v>4.81</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>5.21</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46014.38541666666</v>
+        <v>46014.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>255.65</v>
+        <v>257</v>
       </c>
       <c r="I55" t="n">
         <v>256.9218912040922</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K55" t="n">
-        <v>0.33</v>
+        <v>-0.19</v>
       </c>
       <c r="L55" t="n">
         <v>1.09</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>5.24</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46030.55208333334</v>
+        <v>46031.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>257.1</v>
+        <v>253.8</v>
       </c>
       <c r="I56" t="n">
         <v>257.073344759633</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>16</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K56" t="n">
-        <v>0.04</v>
+        <v>-1.25</v>
       </c>
       <c r="L56" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="M56" t="n">
         <v>0.33</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>6.16</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46057.38541666666</v>
+        <v>46057.55208333334</v>
       </c>
       <c r="H57" t="n">
-        <v>248.89</v>
+        <v>250</v>
       </c>
       <c r="I57" t="n">
         <v>249.3831550771898</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K57" t="n">
-        <v>1.93</v>
+        <v>1.5</v>
       </c>
       <c r="L57" t="n">
         <v>1.89</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>6.57</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46076.55208333334</v>
+        <v>46077.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>267</v>
+        <v>259.31</v>
       </c>
       <c r="I58" t="n">
         <v>262.5343916806807</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K58" t="n">
-        <v>6.8</v>
+        <v>3.72</v>
       </c>
       <c r="L58" t="n">
         <v>0.5</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>7.23</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46114.55208333334</v>
+        <v>46118.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>245.82</v>
+        <v>251.78</v>
       </c>
       <c r="I59" t="n">
         <v>250.6059554717433</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K59" t="n">
-        <v>5.2</v>
+        <v>2.9</v>
       </c>
       <c r="L59" t="n">
         <v>4.08</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46181.38541666666</v>
+        <v>46181.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>261.65</v>
+        <v>258.75</v>
       </c>
       <c r="I60" t="n">
         <v>260.0562550028772</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>63</v>
+        <v>63.16666666666666</v>
       </c>
       <c r="K60" t="n">
-        <v>3.92</v>
+        <v>2.77</v>
       </c>
       <c r="L60" t="n">
         <v>3.36</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>6.14</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>272.9</v>
+        <v>273.9</v>
       </c>
       <c r="I61" t="n">
         <v>273.4704298559658</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>4</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K61" t="n">
-        <v>-5.47</v>
+        <v>-5.86</v>
       </c>
       <c r="L61" t="n">
-        <v>6.53</v>
+        <v>7.27</v>
       </c>
       <c r="M61" t="n">
         <v>1.69</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>5.34</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46244.38541666666</v>
+        <v>46244.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>329</v>
+        <v>323.7</v>
       </c>
       <c r="I62" t="n">
         <v>324.7417527481674</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>56</v>
+        <v>56.16666666666666</v>
       </c>
       <c r="K62" t="n">
-        <v>20.12</v>
+        <v>18.18</v>
       </c>
       <c r="L62" t="n">
         <v>1.33</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>6.03</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46259.55208333334</v>
+        <v>46260.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>332.35</v>
+        <v>337.2</v>
       </c>
       <c r="I63" t="n">
         <v>336.4487323092052</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K63" t="n">
-        <v>-2.67</v>
+        <v>-4.17</v>
       </c>
       <c r="L63" t="n">
-        <v>3.54</v>
+        <v>4.39</v>
       </c>
       <c r="M63" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="N63" t="n">
-        <v>1.32</v>
+        <v>2</v>
       </c>
       <c r="O63" t="n">
         <v>-2.34</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>4.52</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46280.55208333334</v>
+        <v>46281.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>338.3</v>
+        <v>325.75</v>
       </c>
       <c r="I64" t="n">
         <v>330.6416649821161</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K64" t="n">
-        <v>0.33</v>
+        <v>-3.4</v>
       </c>
       <c r="L64" t="n">
-        <v>2.21</v>
+        <v>4.05</v>
       </c>
       <c r="M64" t="n">
         <v>0.62</v>
       </c>
       <c r="N64" t="n">
-        <v>1.63</v>
+        <v>2.75</v>
       </c>
       <c r="O64" t="n">
         <v>2</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>6.72</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46288.38541666666</v>
+        <v>46288.55208333334</v>
       </c>
       <c r="H65" t="n">
-        <v>339</v>
+        <v>339.9</v>
       </c>
       <c r="I65" t="n">
         <v>339.3655602841293</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K65" t="n">
-        <v>-4.07</v>
+        <v>-4.34</v>
       </c>
       <c r="L65" t="n">
-        <v>4.14</v>
+        <v>4.45</v>
       </c>
       <c r="M65" t="n">
         <v>0.59</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>4.94</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46295.38541666666</v>
+        <v>46295.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>327.15</v>
+        <v>321.95</v>
       </c>
       <c r="I66" t="n">
         <v>323.0998812443378</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K66" t="n">
-        <v>-3.75</v>
+        <v>-5.28</v>
       </c>
       <c r="L66" t="n">
         <v>6.08</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>6.1</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46296.55208333334</v>
+        <v>46300.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>324.05</v>
+        <v>341.4</v>
       </c>
       <c r="I67" t="n">
         <v>338.4602452084529</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K67" t="n">
-        <v>-0.65</v>
+        <v>-6.04</v>
       </c>
       <c r="L67" t="n">
-        <v>1.85</v>
+        <v>7.02</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N67" t="n">
-        <v>0.65</v>
+        <v>4.35</v>
       </c>
       <c r="O67" t="n">
         <v>-1.35</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>7.11</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46314.55208333334</v>
+        <v>46316.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>335.4</v>
+        <v>324.45</v>
       </c>
       <c r="I68" t="n">
         <v>327.2436683311597</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K68" t="n">
-        <v>-1.76</v>
+        <v>-4.96</v>
       </c>
       <c r="L68" t="n">
-        <v>2.9</v>
+        <v>5.05</v>
       </c>
       <c r="M68" t="n">
         <v>0.88</v>
       </c>
       <c r="N68" t="n">
-        <v>2.53</v>
+        <v>3.1</v>
       </c>
       <c r="O68" t="n">
         <v>4.35</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4377,6 +5204,12 @@
       <c r="Q69" t="n">
         <v>10</v>
       </c>
+      <c r="R69" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6479,7 +7312,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -6489,7 +7322,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.2</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="7">
@@ -6499,7 +7332,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>119.8</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8">
@@ -6509,7 +7342,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -6519,7 +7352,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35.1</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="10">
@@ -6529,7 +7362,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>57.6</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11">
@@ -6569,7 +7402,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.37</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="15">
@@ -6579,7 +7412,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.28</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="16">
@@ -6589,7 +7422,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.47</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="17">
@@ -6599,7 +7432,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22.47</v>
+        <v>20.54</v>
       </c>
     </row>
     <row r="18">
@@ -6609,7 +7442,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49.3</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="19">
@@ -6619,7 +7452,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.46</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="20">
@@ -6629,7 +7462,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.81</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="21">
@@ -6639,7 +7472,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18.04</v>
+        <v>28.99</v>
       </c>
     </row>
     <row r="22">
@@ -6649,7 +7482,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23">
@@ -6659,7 +7492,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
@@ -6669,7 +7502,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="25">
@@ -6689,7 +7522,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.17</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="27">
@@ -6709,7 +7542,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29">
